--- a/data/satisfaction_detail/2026/6月/自助餐.xlsx
+++ b/data/satisfaction_detail/2026/6月/自助餐.xlsx
@@ -520,7 +520,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>菜品口味口相</t>
+          <t>菜品口味品相</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
